--- a/docs/files/rocscience/vp039c.xlsx
+++ b/docs/files/rocscience/vp039c.xlsx
@@ -13432,10 +13432,10 @@
         <v>0.0</v>
       </c>
       <c r="AF10" s="3">
-        <v>0.0</v>
+        <v>100000.0</v>
       </c>
       <c r="AG10" s="3">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.2">
@@ -13541,10 +13541,10 @@
         <v>0.0</v>
       </c>
       <c r="AF11" s="3">
-        <v>0.0</v>
+        <v>100000.0</v>
       </c>
       <c r="AG11" s="3">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.2">
